--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_06_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_06_21_Cau.xlsx
@@ -1073,7 +1073,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
@@ -1087,7 +1091,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính từng cost component trước khi cộng.</t>
+          <t>Tổng direct evaluation cost: (500 checks * $0) + (200 judge calls * $0,02) + (20 human reviews * $2) = $0 + $4 + $40 = 44 USD.</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1179,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một aggregate win có thể che regression nào?</t>
+          <t>Điều kiện cần thiết của một release gate có thể tái lập: (a) Khóa phiên bản baseline và bộ test suite, (b) so sánh chênh lệch metric trên cùng tập ca kiểm thử (paired delta), (c) đặt ngưỡng bắt buộc cho các phân khúc trọng yếu (critical slice) và an toàn, (d) có quy tắc rõ ràng xử lý độ không chắc chắn.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_06_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_06_21_Cau.xlsx
@@ -624,10 +624,25 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đọc hướng và uncertainty tách biệt.
-Phân tích theo nguyên lý thiết kế: Đọc hướng và uncertainty tách biệt.</t>
+- 1.0đ: Trình bày chuẩn xác dữ liệu các cặp bất đồng: $b=34$ (hồi quy) và $c=44$ (tiến bộ).
+- 1.0đ: Diễn giải đúng $p$-value = 0.31 &gt; 0.05: không có ý nghĩa thống kê, không thể bác bỏ $H_0$.
+- 1.0đ: Phân tích giới hạn thống kê: không thể suy diễn là hai phiên bản tương đương nhau.
+- 1.0đ: Vạch trần điểm mù về mức độ nghiêm trọng của 34 ca hồi quy (rủi ro nghiệp vụ/an toàn tiềm ẩn).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Diễn giải Kết quả Kiểm định McNemar (Interpretation of McNemar Test Results):
+- Dữ liệu kiểm định trên 78 cặp bất đồng (Discordant Pairs):
+  + Số ca phiên bản Cũ đỗ nhưng Mới trượt ($b$ - Old Pass, New Fail): $b = 34$ ca (Hồi quy tiêu cực).
+  + Số ca phiên bản Cũ trượt nhưng Mới đỗ ($c$ - Old Fail, New Pass): $c = 44$ ca (Cải tiến tích cực).
+  + Mức tăng điểm danh nghĩa: $c - b = 44 - 34 = +10$ ca cải tiến.
+- **Kết quả Thống kê Chính xác (Exact Binomial Two-sided Test)**: Đề bài cung cấp $p = 0.31$.
+- **Kết luận Thống kê Chính thức**: Với mức ý nghĩa chuẩn $\alpha = 0.05$, vì $p = 0.31 &gt; 0.05$,   chúng ta **KHÔNG THỂ BÁC BỎ GIẢ THUYẾT KHÔNG ($H_0$)** (Fail to reject $H_0$).   Sự chênh lệch giữa 44 ca tiến bộ và 34 ca hồi quy **hoàn toàn KHÔNG CÓ Ý NGHĨA THỐNG KÊ** (Not Statistically Significant).   Sự cải thiện danh nghĩa 10 ca hoàn toàn có thể chỉ là do may rủi ngẫu nhiên của mẫu thử.
+2. Giới hạn Kỹ thuật Cần Lưu ý (Limitations &amp; Operational Risks):
+- **Cạm bẫy 'Không có bằng chứng không đồng nghĩa với bằng chứng không có' (Absence of Evidence is not Evidence of Absence)**: Kết quả $p = 0.31$ chỉ chứng minh chúng ta chưa đủ dữ liệu để khẳng định V2 tốt hơn, chứ không chứng minh V2 và V1 có chất lượng ngang nhau.
+- **Rủi ro Hồi quy Lớn (Regression Severity Blind Spot)**: McNemar chỉ đếm số lượng ca ($34$ ca hồi quy vs $44$ ca tiến bộ), nhưng hoàn toàn không đo lường mức độ nghiêm trọng của lỗi. Nếu 34 ca V1-pass/V2-fail là các ca rò rỉ bảo mật hoặc vi phạm pháp lý nghiêm trọng, trong khi 44 ca tiến bộ chỉ là sửa lỗi chính tả nhỏ, thì phiên bản V2 thực chất là một bước lùi thảm họa về mặt nghiệp vụ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kiểm định McNemar cho Dữ liệu Cặp Phân loại (McNemar's Test for Paired Nominal Data): Khi so sánh hai mô hình trên cùng một tập benchmark, McNemar là phép kiểm định chuẩn xác nhất vì nó tập trung vào các cặp bất đồng ($b$ và $c$). Khi $p$-value lớn hơn 0.05, về mặt toán học không được phép khẳng định mô hình mới đã cải tiến. Đồng thời, cần kết hợp phân tích định tính mức độ nghiêm trọng của 34 ca hồi quy để tránh việc release các lỗi an toàn nguy hiểm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Quinn McNemar: Note on the sampling error of the difference between strongly correlated proportions (Psychometrika 1947) &amp; Thomas Dietterich: Approximate Statistical Tests for Comparing Supervised Learning Algorithms</t>
         </is>
       </c>
     </row>
@@ -754,10 +769,25 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Recommendation phải phản ánh cả value và uncertainty.
-Phân tích theo nguyên lý thiết kế: Recommendation phải phản ánh cả value và uncertainty.</t>
+- 1.0đ: Phân tích thấu đáo xung đột giữa tính bất định thống kê (CI [-1, +9]) và lợi ích thực tiễn (giảm 20% cost, +4% pass).
+- 1.0đ: Đưa ra quyết định phát hành có điều kiện theo mô hình Canary phân tầng hợp lý, dứt khoát.
+- 1.0đ: Thiết lập điều kiện rào chắn tự động ngắt tải và hoàn nguyên (auto-rollback circuit breaker) khi có sự cố.
+- 1.0đ: Quy định lộ trình thu thập thêm dữ liệu để thu hẹp khoảng tin cậy và mở rộng kiểm thử critical slice.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Khuyến nghị Phát hành có Điều kiện (Conditional Release Recommendation) Cân bằng giữa Thống kê và Thực tiễn:
+1. **Đánh giá Đa chiều giữa Ý nghĩa Thống kê và Giá trị Thực tiễn (Statistical vs Practical Trade-offs)**:
+- **Về mặt Thống kê**: Mặc dù điểm ước lượng tăng $+4\%$, nhưng Khoảng tin cậy 95% delta vẫn chứa giá trị âm: $\text{CI} = [-1\%, +9\%]$. Nghĩa là về mặt thống kê khắt khe, vẫn tồn tại rủi ro nhỏ candidate thực chất làm giảm nhẹ $1\%$ tỷ lệ thành công.
+- **Về mặt Giá trị Thực tiễn Kinh doanh (Practical Business Impact)**: Candidate mang lại lợi ích tài chính khổng lồ: **giảm tới 20% tổng chi phí vận hành**; đồng thời trên tập mẫu lát cắt nhạy cảm (critical slice), candidate hoàn toàn không ghi nhận bất kỳ ca hồi quy nào (Zero observed regression).
+2. **Quyết định Phát hành có Điều kiện (Conditional Canary Go-Decision)**:
+- **Quyết định**: **CHO PHÉP PHÁT HÀNH CÓ ĐIỀU KIỆN THEO MÔ HÌNH CANARY PHÂN TẦNG (CONDITIONAL CANARY ROLLOUT)**. Tuyệt đối không phát hành 100% ngay lập tức, nhưng cũng không từ chối bỏ lỡ khoản tiết kiệm 20% chi phí.
+3. **Các Điều kiện Tiên quyết Bắt buộc khi Triển khai (Prerequisite Conditions)**:
+- **Điều kiện 1: Phân bổ Lưu lượng Thận trọng**: Triển khai Canary theo lộ trình: $2\% \to 10\% \to 25\% \to 100\%$. Giữ mức 2% và 10% tối thiểu 48 giờ để thu thập thêm dữ liệu thực tế nhằm thu hẹp khoảng tin cậy của delta về khoảng hoàn toàn dương.
+- **Điều kiện 2: Chốt chặn Giám sát Tự động (Automated Circuit Breaker / Rollback Gate)**: Cài đặt hệ thống tự động hoàn nguyên (Auto-rollback) trong vòng 60 giây nếu phát hiện tỷ lệ lỗi trên critical slice tăng quá $0.1\%$ hoặc tỷ lệ phàn nàn của người dùng tăng đột biến trong bất kỳ khung giờ nào.
+- **Điều kiện 3: Tiếp tục Mở rộng Mẫu Critical Slice**: Bổ sung thêm 100 ca thử nghiệm vào critical slice trong offline pipeline để củng cố độ tin cậy an toàn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quyết định Phát hành trong SRE (Statistical vs Practical Significance in Release Decisions): Trong kinh doanh phần mềm thực tế, một quyết định không thể chỉ nhìn chăm chăm vào $p$-value hay CI. Một bản cập nhật giảm được 20% chi phí hạ tầng trong khi điểm năng lực có xu hướng tăng (+4%) và chưa thấy lỗi an toàn là một cơ hội lớn. Giải pháp kỹ nghệ trưởng thành là kết hợp giữa 'Sự thận trọng thống kê' và 'Lợi ích thực tiễn' thông qua cơ chế phát hành Canary có giám sát tự động ngắt tải.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Ronny Kohavi, Diane Tang, Ya Xu: Trustworthy Online Controlled Experiments: A Practical Guide to A/B Testing &amp; Google SRE Release Engineering</t>
         </is>
       </c>
     </row>
@@ -840,10 +870,26 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tool selection phải có exit path và evidence cùng benchmark.
-Phân tích theo nguyên lý thiết kế: Tool selection phải có exit path và evidence cùng benchmark.</t>
+- 1.0đ: Thiết kế Kiến trúc Chính hoàn chỉnh kết hợp Ragas (RAG metrics), Pytest (CI assertions) và OpenTelemetry.
+- 1.0đ: Thiết kế Kiến trúc Dự phòng khả thi sử dụng giải pháp self-hosted mã nguồn mở (Langfuse/Phoenix).
+- 1.0đ: Thiết lập hợp đồng chống vendor lock-in ở tầng code ứng dụng (chỉ dùng OTLP chuẩn, không import vendor SDK).
+- 1.0đ: Chuẩn hóa định dạng dữ liệu đánh giá dạng mở (JSONL, Parquet, Git) bảo đảm tính di động dữ liệu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Kiến trúc Đánh giá Chính và Dự phòng (Primary vs Fallback Evaluation Architecture) Không bị Khóa Chặt Nhà cung cấp (Zero Lock-in):
+1. **Kiến trúc Chính: Ngăn xếp Mã nguồn Mở Tách rời Trung lập (Primary Architecture: Decoupled Open-Source Stack)**:
+- **Tầng Offline RAG Metrics**: Sử dụng thư viện mã nguồn mở chuyên dụng **Ragas** (hoặc DeepEval) chạy trực tiếp trong môi trường Python nội bộ để đo lường 4 chỉ số cốt lõi: Faithfulness, Answer Relevance, Context Precision, và Context Recall.
+- **Tầng CI Test Assertions**: Tích hợp trực tiếp vào **Pytest** chạy trong GitHub Actions / GitLab CI. Viết các bài test assertion định lượng: `assert score['faithfulness'] &gt;= 0.85`, chạy trên tập Golden Dataset được phiên bản hóa bằng Git-LFS/DVC.
+- **Tầng Production Trace Feedback**: Triển khai **OpenTelemetry Python SDK** với các chuẩn semantic conventions cho GenAI. Toàn bộ spans, tokens, độ trễ và user feedback được phát thải qua giao thức mở **OTLP (OpenTelemetry Protocol)** chuẩn quốc tế.
+2. **Kiến trúc Dự phòng / Tự lưu trữ (Fallback Architecture: Self-Hosted Platform)**:
+- Khi cần một giao diện trực quan hóa chuyên nghiệp mà không phụ thuộc SaaS đám mây: Triển khai cụm **Langfuse Self-Hosted** (hoặc Arize Phoenix Self-Hosted) trên Kubernetes nội bộ.
+- **Khả năng chuyển đổi mượt mà**: Vì cả Langfuse và Phoenix đều hỗ trợ tiếp nhận dữ liệu chuẩn OpenTelemetry OTLP, ứng dụng không cần sửa code; chỉ cần cấu hình endpoint OTel Collector trỏ tới instance nội bộ này.
+3. **Hợp đồng Chống Khóa Chặt (Zero Lock-in Contract)**:
+- Code ứng dụng tuyệt đối **KHÔNG IMPORT** các SDK độc quyền đóng kín của bên thứ ba (như Proprietary Vendor Wrappers).
+- Toàn bộ dữ liệu benchmark, prompt templates và kết quả đánh giá được lưu trữ dưới dạng file chuẩn mở: **JSONLines / Parquet / Git**, bảo đảm có thể chuyển đổi sang bất kỳ nền tảng nào trong tương lai chỉ trong vòng 1 ngày làm việc.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Lựa chọn Khung Đánh giá AI (Framework Selection &amp; Anti-Lock-in Architecture): Thị trường công cụ đánh giá AI thay đổi rất nhanh; việc lệ thuộc vào một nền tảng SaaS độc quyền đóng kín sẽ đẩy doanh nghiệp vào thế rủi ro tăng giá và rò rỉ dữ liệu. Một kiến trúc chuẩn mực phải xây dựng trên các trụ cột mở: Ragas cho thuật toán chấm điểm, Pytest cho đường ống CI/CD, và OpenTelemetry cho tầng thu thập dữ liệu sản xuất. Dữ liệu chuẩn mở bảo đảm quyền tự chủ công nghệ vĩnh viễn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RAGAS Documentation (https://docs.ragas.io) &amp; OpenTelemetry GenAI Semantic Conventions &amp; CNCF Open Source Standards</t>
         </is>
       </c>
     </row>
@@ -922,10 +968,32 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Decision đa mục tiêu cần constraint theo service context.
-Phân tích theo nguyên lý thiết kế: Decision đa mục tiêu cần constraint theo service context.</t>
+- 1.0đ: Phân tích đúng bản chất của Pareto Frontier: không có giải pháp duy nhất hoàn hảo, bắt buộc phải đánh đổi.
+- 1.0đ: Xác định đầy đủ các dữ kiện ràng buộc kỹ thuật/tài chính cho Free Tier (trần chi phí, sàn chất lượng tối thiểu).
+- 1.0đ: Xác định đầy đủ các dữ kiện ràng buộc nghiêm ngặt cho Premium Tier (cam kết chất lượng cao, P95 latency nhanh).
+- 1.0đ: Thiết lập quy trình 2 bước lựa chọn điểm vận hành tách biệt tối ưu cho từng phân khúc dịch vụ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Quy trình và Dữ kiện Cần thiết để Chọn Điểm Vận hành (Operating Point Selection) trên Pareto Frontier cho Từng Phân khúc (Free vs Premium):
+1. **Bản chất của Đường biên Pareto (Pareto Frontier Dilemma)**:
+Ba kiến trúc AI đều nằm trên Pareto Frontier nghĩa là không có kiến trúc nào tối ưu toàn diện (Architecture A: Chất lượng cao nhất nhưng Rất đắt và Chậm; Architecture B: Siêu nhanh và Rẻ nhưng Chất lượng trung bình; Architecture C: Cân bằng vừa phải). Không thể chọn một giải pháp duy nhất cho mọi đối tượng người dùng.
+2. **Dữ kiện Cần Thu thập để Xác lập Ràng buộc cho Từng Tier (Required Data &amp; Constraints)**:
+- **Dữ kiện cho Gói Miễn phí (Free Tier Data &amp; Constraints)**:
+  + *Trần Chi phí Tối đa cho phép (Cost Ceiling)*: Biên độ tài chính cho phép bù lỗ marketing (ví dụ: $\le 0.002$ USD/request).
+  + *Ngưỡng Sàn Chất lượng Tối thiểu (Minimum Quality Floor)*: Mức độ chính xác chấp nhận được để người dùng không bỏ app (ví dụ: Quality Score $\ge 75\%$).
+  + *SLA Độ trễ (P95 Latency SLA)*: Chấp nhận độ trễ vừa phải, ví dụ P95 $\le 4.0$ giây.
+- **Dữ kiện cho Gói Trả phí Doanh nghiệp (Premium Tier Data &amp; Constraints)**:
+  + *Hợp đồng Cam kết Chất lượng Tuyệt đối (Quality Contract)*: Bắt buộc đạt chuẩn Enterprise (ví dụ: Quality Score $\ge 92\%$).
+  + *SLA Độ trễ Nghiêm ngặt (Strict Latency SLA)*: Thời gian phản hồi streaming tức thì, P95 $\le 1.5$ giây, TTFT $\le 0.5$ giây.
+  + *Biên Lợi nhuận Mục tiêu (Target Unit Economics)*: Doanh thu gói đủ bù đắp chi phí mô hình đắt đỏ (ví dụ: chi phí có thể lên tới 0.03 USD/request vì user trả 50 USD/tháng).
+3. **Quy trình Lựa chọn Điểm Vận hành Cụ thể (Operating Point Selection Workflow)**:
+- **Bước 1**: Áp dụng bộ lọc ràng buộc cứng (Hard Filtering): Loại bỏ các kiến trúc vi phạm trần chi phí của Free Tier và vi phạm sàn chất lượng của Premium Tier.
+- **Bước 2: Gán Điểm Vận hành Tối ưu cho Từng Tier**:
+  + **Gói Free Tier -&gt; Chọn Architecture B (SLM / Quantized Model)**: Tối ưu hóa tối đa chi phí và thông lượng, bảo đảm không làm vỡ quỹ tài chính.
+  + **Gói Premium Tier -&gt; Chọn Architecture A (Frontier LLM / High-compute RAG)**: Tối ưu hóa tối đa độ chính xác và trải nghiệm mượt mà để bảo vệ doanh thu thuê bao trả phí.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Tối ưu Đa mục tiêu và Phân đoạn Dịch vụ (Multi-objective Pareto Optimization &amp; Service Tiering): Cố gắng ép toàn bộ khách hàng dùng chung một kiến trúc là sai lầm kinh điển: dùng mô hình xịn cho free user sẽ phá sản vì chi phí token; dùng mô hình rẻ cho enterprise user sẽ mất khách hàng vì chất lượng kém. Bằng cách xác định rõ các ràng buộc kỹ thuật và tài chính độc lập cho từng phân khúc người dùng, doanh nghiệp có thể chọn hai điểm vận hành hoàn toàn khác nhau trên cùng một đường biên Pareto.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pareto Efficiency in Systems Engineering &amp; FinOps Foundation: Managing Unit Economics for GenAI</t>
         </is>
       </c>
     </row>
@@ -1004,10 +1072,31 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ đúng denominator stage của từng metric.
-Phân tích theo nguyên lý thiết kế: Giữ đúng denominator stage của từng metric.</t>
+- 1.0đ: Tính đúng Tốc độ sinh token: $\text{TPS} = 180 / 12 = 15.0$ tokens/giây.
+- 1.0đ: Diễn giải đúng bản chất của TTFT 0.8s đối với độ phản ứng ban đầu của giao diện streaming.
+- 1.0đ: Diễn giải đúng ý nghĩa của TPS 15.0 tokens/s so với tốc độ đọc tự nhiên của con người.
+- 1.0đ: Phân tích cấu trúc Total Task Latency 15s và chỉ ra khoản thời gian overhead 2.2s cần tối ưu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Tốc độ Sinh Token (Tokens Per Second - TPS):
+- Dữ liệu bài toán:
+  + Thời gian đến token đầu tiên: $\text{TTFT} = 0.8$ giây.
+  + Số lượng token sinh thêm sau token đầu tiên: $N_{\text{subsequent\_tokens}} = 180$ tokens.
+  + Thời gian tiêu tốn để sinh 180 tokens đó: $\Delta t_{\text{generation}} = 12$ giây.
+  + Tổng thời gian tác vụ hoàn chỉnh: $T_{\text{total}} = 15$ giây.
+- **Công thức tính Tốc độ Sinh Token (Generation TPS)**:
+  $$\text{TPS} = \frac{N_{\text{subsequent\_tokens}}}{\Delta t_{\text{generation}}} = \frac{180 \text{ tokens}}{12 \text{ giây}} = \mathbf{15.0 \text{ tokens/giây}}$$
+  *(Lưu ý kỹ thuật: Mẫu số của TPS thế hệ chỉ tính thời gian sinh thực tế 12s, không lấy tổng thời gian 15s)*.
+2. Diễn giải Ý nghĩa Kỹ thuật và Trải nghiệm của Ba Chỉ số (Three Metrics Interpretation):
+- **TTFT (Time to First Token = 0.8s - Độ phản ứng ban đầu)**:
+  + *Ý nghĩa*: Đo lường thời gian từ lúc người dùng gửi yêu cầu đến khi nhìn thấy ký tự đầu tiên xuất hiện trên màn hình streaming UI.   Mức 0.8s là xuất sắc (dưới 1s), tạo cho người dùng cảm giác hệ thống cực kỳ nhanh nhạy và không bị đơ giật.
+- **TPS (Tokens Per Second = 15.0 tokens/s - Nhịp điệu đọc trực quan)**:
+  + *Ý nghĩa*: Đo lường tốc độ dòng chảy của văn bản được sinh ra. Tốc độ đọc trung bình của người bình thường là khoảng 4 - 5 từ/giây (tương đương 6 - 8 tokens/giây).   Tốc độ 15 tokens/s nhanh hơn tốc độ đọc của mắt người khoảng 2 lần, bảo đảm văn bản hiển thị mượt mà liên tục, không gây ức chế chờ từng từ.
+- **Total Task Latency (= 15.0s - Thời gian Hoàn tất Tác vụ)**:
+  + *Ý nghĩa*: Đo lường tổng thời gian người dùng phải chờ để toàn bộ câu trả lời hoàn thành trọn vẹn.   Phân tích cấu trúc thời gian: $15.0s = 0.8s \text{ (TTFT)} + 12.0s \text{ (Sinh token)} + 2.2s \text{ (Thời gian dư thừa/Overhead)}$.   Khoảng dôi dư 2.2s này chỉ ra độ trễ mạng sau cùng, thời gian đóng kết nối, hoặc bước validation kết quả cần được tối ưu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hệ thống Chỉ số Độ trễ trong Ứng dụng GenAI Streaming (TTFT, TPS, and E2E Latency): Trong phần mềm truyền thống, chỉ có một chỉ số độ trễ duy nhất (Total Latency). Trong GenAI với giao diện Streaming, trải nghiệm người dùng phụ thuộc sâu sắc vào TTFT (giảm cảm giác chờ đợi ban đầu) và TPS (duy trì nhịp đọc mượt mà). Phân tích bóc tách cả 3 chỉ số giúp kỹ sư xác định chính xác nút thắt cổ chai nằm ở khâu TTFT (prompt processing/prefill) hay ở khâu TPS (decoding speed) hay ở overhead sau cùng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+vLLM Documentation: Performance Metrics &amp; Cloudflare: Understanding TTFT and Generation Speed in LLM Inference</t>
         </is>
       </c>
     </row>
@@ -1122,10 +1211,39 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng double-count hoặc âm thầm bỏ escalation.
-Phân tích theo nguyên lý thiết kế: Đừng double-count hoặc âm thầm bỏ escalation.</t>
+- 1.0đ: Tính đúng chi phí Judge: 2.000 ca $\times 0.01 = 20.00$ USD.
+- 1.0đ: Tính đúng chi phí Human Base: 200 ca $\times 1.50 = 300.00$ USD.
+- 1.0đ: Tính đúng chi phí Human Escalated: 100 ca $\times 1.50 = 150.00$ USD và tổng chi phí chính xác 470.00 USD.
+- 1.0đ: Đưa ra đề xuất tiết kiệm chi phí khả thi (Cascaded SLM pre-filter, semantic caching) mà không suy giảm độ bao phủ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Chi phí Trực tiếp Đánh giá Tập 10.000 Ca (Direct Evaluation Cost Calculation):
+- Tổng số ca đánh giá: $N = 10.000$ ca.
+- **Thành phần 1: Deterministic Rule Checks (100% ca)**:
+  + Đơn giá: $0.00 USD (chạy code Python/Regex nội bộ, chi phí tính toán không đáng kể).
+  + Chi phí = $10.000 \times 0 = \mathbf{0.00 \text{ USD}}$.
+- **Thành phần 2: LLM-as-a-Judge Đánh giá Tự động (20% ca)**:
+  + Số ca cần judge: $10.000 \times 20\% = 2.000$ ca.
+  + Đơn giá judge: $0.01 USD/ca.
+  + Chi phí Judge = $2.000 \times 0.01 = \mathbf{20.00 \text{ USD}}$.
+- **Thành phần 3: Chuyên gia Con người Cơ sở (Base Human Review - 2% ca)**:
+  + Số ca cơ sở: $10.000 \times 2\% = 200$ ca.
+  + Đơn giá chuyên gia: $1.50 USD/ca.
+  + Chi phí Human Base = $200 \times 1.50 = \mathbf{300.00 \text{ USD}}$.
+- **Thành phần 4: Ca Không Chắc chắn từ Judge Leo thang lên Con người (Judge Uncertain Escalation)**:
+  + Đề bài nêu: 5% số ca Judge xử lý bị bất định và leo thang lên human review (nằm ngoài 2% base).
+  + Số ca leo thang = $2.000 \times 5\% = 100$ ca.
+  + Chi phí Human Escalated = $100 \times 1.50 = \mathbf{150.00 \text{ USD}}$.
+- **TỔNG CHI PHÍ TRỰC TIẾP (TOTAL DIRECT EVALUATION COST)**:
+  $$\text{Total Cost} = 0.00 + 20.00 + 300.00 + 150.00 = \mathbf{470.00 \text{ USD}}$$
+2. Đề xuất Tiết kiệm Chi phí mà Không Làm Suy giảm Độ bao phủ Cam kết (Cost-saving Strategy):
+- **Nhận diện trọng tâm chi phí**: Chi phí con người chiếm tới $450 / 470 = 95.7\%$ tổng ngân sách! Mọi nỗ lực tối ưu hóa phải tập trung vào việc giảm thiểu giờ làm của con người mà không bỏ sót lỗi.
+- **Đề xuất Tiết kiệm: Thiết kế Kiến trúc Lọc Tầng Phân cấp (Cascaded Tiered Evaluation)**:
+  + **Mô hình Judge Nhỏ Trước (SLM Pre-filter)**: Đối với 100 ca Judge bị bất định, thay vì lập tức chuyển sang con người với giá $1.50,   cho chạy qua một prompt thứ hai với cơ chế CoT (Chain-of-Thought) hoặc một mô hình Judge thứ hai (chi phí $0.02).   Thực nghiệm cho thấy phương pháp này giải quyết được 60% ca bất định mà không cần con người, giúp tiết kiệm $60 \times 1.50 = 90$ USD.
+  + **Lưu đệm Kết quả Đánh giá (Semantic Eval Caching)**: Lưu cache các câu trả lời trùng lặp hoặc tương đương ngữ nghĩa để không phải gọi Judge và Human nhiều lần, giúp giảm tổng chi phí thêm 15-20% mà giữ nguyên 100% độ bao phủ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản trị Chi phí trong Đánh giá AI (FinOps for LLM Evaluation): Chi phí chuyên gia con người luôn đắt gấp hàng trăm lần chi phí mô hình (ở đây $1.50 so với $0.01 là gấp 150 lần). Tính toán đầy đủ cả các chi phí leo thang (escalation costs) là bắt buộc để lập ngân sách chính xác. Áp dụng cơ chế lọc tầng thông minh (Tiered Cascade) giúp tận dụng tối đa sức mạnh của tự động hóa rẻ tiền trước khi phải cầu viện tới nguồn lực con người đắt đỏ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+FinOps Foundation Framework &amp; FrugalGPT: How to Use Large Language Models More Affordably (Chen et al., Stanford 2023)</t>
         </is>
       </c>
     </row>
@@ -1210,10 +1328,30 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Gate là decision contract, không phải score summary.
-Phân tích theo nguyên lý thiết kế: Gate là decision contract, không phải score summary.</t>
+- 1.0đ: Áp dụng đầy đủ và chính xác các cổng kiểm soát (Cost, North-star, Safety slice).
+- 1.0đ: Đưa ra phán quyết dứt khoát: HARD BLOCK / NO-GO dựa trên sự vi phạm của lát cắt an toàn (-3% vs -1%).
+- 1.0đ: Khẳng định nguyên tắc phủ quyết của lát cắt an toàn bất chấp điểm tổng thể tăng và chi phí đạt.
+- 1.0đ: Liệt kê đầy đủ các hành động tất định trên hệ thống (block CI/CD, auto-create P0 ticket, export diagnostic package).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Áp dụng Cổng Kiểm soát Hồi quy (Application of Regression Release Gates):
+- **Đánh giá Cổng 1: Ngân sách Chi phí (Cost Budget Gate)** -&gt; **PASS**: Chi phí đạt ngân sách cho phép.
+- **Đánh giá Cổng 2: Chỉ số Ngôi sao Phương Bắc Tổng thể (North-Star Gate)** -&gt; **CONDITIONAL / WEAK PASS**: Tăng $+2$ điểm nhưng khoảng tin cậy còn rộng.
+- **Đánh giá Cổng 3: Cổng Rào cản An toàn Lát cắt (Safety Slice Hard Gate)** -&gt; **CRITICAL VIOLATION / HARD FAIL**:
+  + Quy tắc cổng an toàn quy định: Ngưỡng trần suy giảm tối đa cho phép là $-1$ điểm phần trăm (Block Threshold = -1).
+  + Thực tế quan sát: Lát cắt an toàn (Safety Slice) bị sụt giảm tới **$-3$ điểm phần trăm** (vượt ngưỡng cho phép gấp 3 lần).
+- **Phán quyết Chung cuộc của Cổng Release**: **HARD BLOCK / NO-GO (CHẶN ĐỨNG PHÁT HÀNH TUYỆT ĐỐI)**.
+  Bất kể điểm tổng thể tăng bao nhiêu hay chi phí rẻ thế nào, một vi phạm vượt ngưỡng trên lát cắt an toàn lập tức kích hoạt quyền phủ quyết tối cao.
+2. Hành động Kỹ thuật Tất định Ghi nhận trên Hệ thống (Deterministic System Actions):
+- **Hành động 1: Tự động Đóng băng Pipeline CI/CD (Pipeline Block)**:
+  Hệ thống CI/CD tự động gắn nhãn trạng thái `BUILD_FAILED_RELEASE_GATE_BREACH`, khóa lệnh merge vào nhánh main, và ngăn chặn việc đẩy container image lên Production Registry.
+- **Hành động 2: Tự động Mở Vé Sự cố Hồi quy (Automated Incident Ticket Creation)**:
+  Hệ thống tự động tạo một Jira Issue mức độ ưu tiên cao nhất (`Severity: P0 - Blocker`), tiêu đề: `[Gate Breach] Safety Slice Regression -3% detected in Candidate V2`.
+- **Hành động 3: Đính kèm Gói Bằng chứng Chẩn đoán (Diagnostic Package Export)**:
+  Tự động xuất danh sách các ca test bị trượt trong lát cắt an toàn kèm diff so sánh câu trả lời giữa baseline và candidate vào ticket Jira, gán trực tiếp cho Tech Lead phụ trách Safety để điều tra.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Cổng Kiểm soát Tất định trong CI/CD (Deterministic Release Gates &amp; Non-negotiable Thresholds): Một cổng kiểm soát phát hành chỉ có ý nghĩa khi nó vận hành như một chiếc rơ-le tự động, không phụ thuộc vào sự thương lượng hay cảm xúc của con người. Khi một lát cắt an toàn bị hồi quy vượt ngưỡng quy định (-3% so với trần -1%), hệ thống phải tự động thực thi các hành động tất định: block pipeline, tạo ticket lỗi và đính kèm bằng chứng để đội ngũ kỹ thuật bắt tay vào sửa lỗi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Release Engineering &amp; Martin Fowler: Deployment Pipelines and Quality Gates</t>
         </is>
       </c>
     </row>
@@ -1296,10 +1434,28 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không đổi agent và evaluator mà thiếu version attribution.
-Phân tích theo nguyên lý thiết kế: Không đổi agent và evaluator mà thiếu version attribution.</t>
+- 1.0đ: Phân tích đúng rủi ro nhiễu khi Candidate khác biệt 18% và Rubric của Judge cũng bị đổi đồng thời.
+- 1.0đ: Tận dụng ưu thế của môi trường Shadow Testing (chưa có rủi ro người dùng thực tế) để kiểm định an toàn.
+- 1.0đ: Thiết kế thử nghiệm bóc tách nguyên nhân (chạy chéo rubric cũ/mới và human review 50 ca diff).
+- 1.0đ: Xây dựng lộ trình triển khai phân tầng (Dogfooding -&gt; Canary 1% -&gt; 5% -&gt; 100%) kèm điều kiện chuyển giai đoạn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Bóc tách Trách nhiệm (Attribution) và Kế hoạch Triển khai Phân tầng Tiếp theo (Staged Rollout Plan):
+1. **Bản chất Thách thức Bóc tách (Attribution Decoupling)**:
+Dữ liệu Shadow Testing cho thấy phiên bản Candidate sinh ra câu trả lời khác biệt tới **18%** so với Baseline, nhưng đồng thời **Rubric của mô hình Judge cũng vừa được nâng cấp phiên bản**. Nếu đánh giá kết quả ngay lúc này, nhóm kỹ sư sẽ rơi vào trạng thái bế tắc: không thể biết 18% khác biệt đó là do Candidate thông minh hơn, hay do Rubric mới chấm lệch chuẩn, hay Candidate đang sinh ra câu trả lời sai lệch nguy hiểm. May mắn là hệ thống đang chạy ở chế độ Shadow (chạy ngầm song song), hoàn toàn chưa có người dùng thực nào tiếp xúc với dữ liệu này (`zero user exposure`).
+2. **Thiết kế Thử nghiệm Bóc tách Nguyên nhân (Decoupled Attribution Experiment)**:
+- Chạy ma trận đánh giá đối chứng 2x2 trên 500 ca mẫu của 18% câu trả lời có sự khác biệt (Semantic Diff Cases):
+  + Lượt 1: Chạy `Candidate` và `Baseline` dưới **Rubric Cũ**.
+  + Lượt 2: Chạy `Candidate` và `Baseline` dưới **Rubric Mới**.
+  + Lượt 3: Lấy ngẫu nhiên 50 ca có sự phân hóa lớn nhất gửi cho **Chuyên gia con người thẩm định mù (Blind Human Review)**.
+- **Xác định Attribution**: Nếu con người và cả hai rubric đều xác nhận 18% câu trả lời mới của Candidate có độ chính xác cao hơn và giải quyết tốt hơn câu hỏi của người dùng, khẳng định 18% khác biệt này là **Tiến bộ Nghiệp vụ Tích cực (Positive Semantic Evolution)**.
+3. **Kế hoạch Triển khai Phân tầng Kế tiếp (Next Staged Rollout Plan)**:
+- **Giai đoạn 1: Internal Dogfooding (Nội bộ 1 tuần)**: Triển khai Candidate cho toàn bộ nhân viên nội bộ công ty sử dụng thử nghiệm trước.
+- **Giai đoạn 2: Canary Phân tầng Nhẹ (1% -&gt; 5% Traffic)**: Mở cho 1% người dùng thật; giám sát chặt chẽ tỷ lệ phàn nàn và lỗi kỹ thuật.
+- **Giai đoạn 3: Mở rộng Toàn diện (25% -&gt; 50% -&gt; 100%)**: Tăng dần lưu lượng sau khi vượt qua các mốc soak time 48 giờ an toàn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thẩm định Chạy ngầm và Triển khai An toàn (Shadow Semantic Diff &amp; Staged Rollout): Chế độ Shadow Testing là một đặc ân tuyệt vời: nó cho phép chúng ta nhìn thấy sự khác biệt ngữ nghĩa 18% mà không làm rủi ro khách hàng. Khi có sự thay đổi kép (cả model lẫn rubric), bắt buộc phải dùng thẩm định chéo và chuyên gia con người để bóc tách rõ nguyên nhân. Sau khi đã chứng minh sự khác biệt là có lợi, lộ trình Canary phân tầng từng bước bảo đảm sự an toàn tối đa cho đợt release.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Canary Releases &amp; Launch Coordination &amp; Martin Fowler: Shadowing Pattern</t>
         </is>
       </c>
     </row>
@@ -1382,10 +1538,32 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không patch từng answer hoặc đổi model chung chung.
-Phân tích theo nguyên lý thiết kế: Không patch từng answer hoặc đổi model chung chung.</t>
+- 1.0đ: Phân rã chuẩn xác 10 ca lỗi thành hai nhánh nguyên nhân độc lập (7 ca Stale Policy và 3 ca Prompt Condition).
+- 1.0đ: Xây dựng chuỗi 5 Whys logic, mạch lạc cho Nhánh A chạm tới căn nguyên Data Lifecycle/Crawler.
+- 1.0đ: Xây dựng chuỗi 5 Whys logic, mạch lạc cho Nhánh B chạm tới căn nguyên Quản trị Thay đổi Prompt/CI Gate.
+- 1.0đ: Thiết lập kế hoạch xác minh khắc phục cụ thể cho cả hai nhánh, bảo đảm tái kiểm thử đạt 100% pass.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Dựng Cây Phân tích Nguyên nhân Gốc 5 Whys (5 Whys Root-Cause Analysis) và Kế hoạch Xác minh Khắc phục (Fix Verification):
+1. **Bóc tách Hai Nhánh Nguyên nhân từ 10 Ca Lỗi 'Wrong Answer'**:
+- **Nhánh A (7 ca: Do truy xuất tài liệu chính sách cũ - Stale Policy)**:
+  + *Tại sao 1 (Why 1)*: Tại sao 7 ca trả lời sai? -&gt; Vì hệ thống RAG truy xuất nhầm văn bản chính sách cũ đã hết hạn.
+  + *Tại sao 2 (Why 2)*: Tại sao lại truy xuất chính sách cũ? -&gt; Vì trong cơ sở dữ liệu Vector DB, các chunks của chính sách cũ vẫn đang tồn tại song song với chính sách mới.
+  + *Tại sao 3 (Why 3)*: Tại sao chính sách cũ không bị xóa hoặc gắn thẻ lưu trữ? -&gt; Vì quy trình nạp dữ liệu (Data Pipeline) không có bước xóa hoặc vô hiệu hóa các phiên bản tài liệu trước đó.
+  + *Tại sao 4 (Why 4)*: Tại sao data pipeline thiếu tính năng quản lý vòng đời tài liệu? -&gt; Vì crawler chỉ thực hiện hành động ghi đè theo tên file, trong khi văn bản mới được đổi tên thành `Chinh_Sach_2026_Final.pdf`.
+  + *Tại sao 5 (Why 5 - Căn nguyên gốc)*: **Quy trình Quản trị Dữ liệu RAG thiếu cơ chế Document Lifecycle &amp; Version Invalidation chuẩn hóa**.
+- **Nhánh B (3 ca: Retrieval đúng nhưng Prompt lược bỏ điều kiện)**:
+  + *Tại sao 1 (Why 1)*: Tại sao 3 ca trả lời sai dù retrieval lấy đúng tài liệu? -&gt; Vì câu trả lời của mô hình bỏ qua điều kiện ngoại lệ quan trọng.
+  + *Tại sao 2 (Why 2)*: Tại sao mô hình bỏ qua điều kiện ngoại lệ? -&gt; Vì System Prompt hướng dẫn mô hình tóm tắt 'ngắn gọn dưới 2 câu' nên mô hình đã tự ý cắt bỏ các điều kiện ràng buộc.
+  + *Tại sao 3 (Why 3)*: Tại sao lại có chỉ thị tóm tắt quá ngắn? -&gt; Vì một kỹ sư đã sửa prompt tuần trước để tối ưu độ dài mà không kiểm thử hồi quy trên các ca có điều kiện phức tạp.
+  + *Tại sao 4 (Why 4)*: Tại sao sửa prompt mà không kiểm thử hồi quy? -&gt; Vì CI/CD chưa có chốt chặn bắt buộc phải chạy bộ test 'complex conditions' trước khi merge prompt.
+  + *Tại sao 5 (Why 5 - Căn nguyên gốc)*: **Thiếu quy trình Kiểm định Hồi quy Bắt buộc (Mandatory Regression Gate) khi thay đổi System Prompt**.
+2. Kế hoạch Xác minh Khắc phục Dứt điểm (Fix Verification Plan):
+- **Khắc phục Nhánh A**: Triển khai trường metadata `is_active: bool` và `version` trong Vector DB; cấu hình retriever chỉ lọc `filter={'is_active': True}`. Chạy lại 7 ca lỗi -&gt; **Xác minh 100% trả về tài liệu mới**.
+- **Khắc phục Nhánh B**: Sửa lại System Prompt nêu rõ: 'Không được phép lược bỏ các điều kiện loại trừ hoặc ngoại lệ dù tóm tắt'. Đưa 3 ca lỗi vào bộ kiểm thử tự động của CI/CD -&gt; **Xác minh 100% câu trả lời chứa đủ điều kiện**.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phương pháp 5 Whys trong Phân tích Sự cố AI (Five Whys Root Cause Analysis): Một triệu chứng bề mặt ('Trả lời sai') thường được tạo thành từ nhiều nhánh nguyên nhân khác nhau. Trong ca này, 70% lỗi do tầng Dữ liệu (Stale index data pipeline) và 30% lỗi do tầng Nhắc lệnh (Prompt over-summarization). Truy tìm đủ 5 tầng nguyên nhân giúp chúng ta không chỉ vá lỗi cục bộ (patch a bug) mà sửa tận gốc quy trình quản trị dữ liệu và quy trình release prompt của tổ chức.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Taiichi Ohno: Toyota Production System (5 Whys Methodology) &amp; Google SRE Postmortem Guidelines</t>
         </is>
       </c>
     </row>
@@ -1468,10 +1646,28 @@
       <c r="K23" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Promotion không được biến một pass thành bằng chứng phổ quát.
-Phân tích theo nguyên lý thiết kế: Promotion không được biến một pass thành bằng chứng phổ quát.</t>
+- 1.0đ: Đưa ra quyết định thăng hạng chuẩn xác: thăng hạng ca đã pass vào Golden Suite để chống hồi quy.
+- 1.0đ: Đưa ra quyết định phát hành dứt khoát: tạm hoãn release do ca lỗi láng giềng đa ngôn ngữ vẫn thất bại.
+- 1.0đ: Phân tích thấu đáo bản chất của lỗi láng giềng (do embedding cross-lingual hoặc thiếu tài liệu dịch).
+- 1.0đ: Thiết lập quy trình xác minh vùng lân cận (neighborhood stress test) và thăng hạng toàn bộ cụm lỗi trước khi release.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Quyết định Thăng hạng Kiểm thử (Promotion Decision) và Quy trình Xác minh Kế tiếp (Next Verification Workflow):
+1. **Đánh giá Tình huống Kỹ thuật Hiện tại**:
+- Sau khi khắc phục lỗi dữ liệu cũ (stale-index fix), ca lỗi đại diện ban đầu (representative failure) đã vượt qua bài test thành công (PASS).
+- Tuy nhiên, một ca kiểm thử láng giềng trong không gian đa ngôn ngữ (Neighboring Multilingual Case - ví dụ cùng câu hỏi nhưng được hỏi bằng Tiếng Anh hoặc Tiếng Pháp) **LẠI BỊ THẤT BẠI (FAIL)**.
+2. **Quyết định Thăng hạng và Quyết định Phát hành (Dual-Decision Contract)**:
+- **Quyết định đối với Ca Đại diện đã Pass**: **CHẤP THUẬN THĂNG HẠNG VÀO REGRESSION SUITE (PROMOTE TO GOLDEN SUITE)**. Ca này đã được sửa thành công và cần được đóng băng thành một test case tự động cố định trong CI/CD để vĩnh viễn không bị tái phát lỗi stale-index.
+- **Quyết định đối với Đợt Phát hành Sản phẩm (Release Decision)**: **TẠM HOÃN PHÁT HÀNH (HOLD / BLOCK RELEASE)**. Tuyệt đối không phát hành phiên bản mới ra thị trường chừng nào ca lỗi đa ngôn ngữ láng giềng chưa được giải quyết triệt để.
+3. **Kế hoạch Xác minh Tiếp theo (Next Systematic Verification Plan)**:
+- **Bước 1 - Phân tích Nguyên nhân Lỗi Láng giềng (Neighboring Gap Analysis)**: Điều tra xem ca đa ngôn ngữ bị fail là do:
+  + Mô hình Embedding đa ngôn ngữ (Multilingual Embedding) có độ tương đồng thấp khi truy vấn cross-lingual?
+  + Hay do tài liệu chính sách mới chỉ được cập nhật bản tiếng Việt mà chưa có bản dịch tiếng Anh trong kho dữ liệu?
+- **Bước 2 - Mở rộng Lưới Kiểm thử Láng giềng (Adjacency Matrix Stress Test)**: Tạo thêm 10-20 biến thể láng giềng tương đương (paraphrases, ngôn ngữ khác, từ đồng nghĩa) để kiểm tra toàn bộ vùng lân cận của lỗ hổng.
+- **Bước 3 - Vá lỗi và Thăng hạng Toàn bộ Cụm (Cluster Promotion)**: Sau khi fix xong, thăng hạng toàn bộ cụm ca láng giềng này vào bộ Golden Suite, sau đó mới chính thức mở cổng release sản phẩm.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Vòng lặp Thăng hạng Kiểm thử và Kiểm tra Láng giềng (Regression Promotion &amp; Neighborhood Invariance): Một sai lầm nguy hiểm trong bảo trì AI là 'vá đâu biết đó' (Whack-a-mole fix): sửa được đúng 1 câu hỏi cụ thể nhưng câu hỏi tương đương bằng tiếng khác vẫn hỏng. Việc một ca láng giềng bị thất bại chứng minh lỗ hổng chưa được xử lý ở cấp độ hệ thống (Systemic Vulnerability). Một quy trình QA chuẩn mực phải vừa giữ lại ca đã pass làm chốt chặn, vừa chặn đứng release để sửa dứt điểm toàn bộ cụm láng giềng liên quan.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+CheckList: Beyond Accuracy: Behavioral Testing of NLP Models with CheckList (Ribeiro et al., ACL 2020) &amp; Google SRE Postmortem Action Tracking</t>
         </is>
       </c>
     </row>
